--- a/jpcore-r4/feature/test-claude-opus/StructureDefinition-jp-diagnosticreport-radiology.xlsx
+++ b/jpcore-r4/feature/test-claude-opus/StructureDefinition-jp-diagnosticreport-radiology.xlsx
@@ -379,7 +379,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -616,7 +616,7 @@
     <t>診断サービスセクションのコード。 / Codes for diagnostic service sections.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/diagnostic-service-sections</t>
+    <t>http://hl7.org/fhir/ValueSet/diagnostic-service-sections|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">value:$this}
@@ -1278,7 +1278,7 @@
     <t>DiagnosticReport.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(Specimen|4.0.1)
 </t>
   </si>
   <si>
@@ -1421,7 +1421,7 @@
     <t>DiagnosticReport.media.link</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Media)
+    <t xml:space="preserve">Reference(Media|4.0.1)
 </t>
   </si>
   <si>
@@ -1481,7 +1481,7 @@
     <t>レポートの補助として提供される診断コード。 / Diagnosis codes provided as adjuncts to the report.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/clinical-findings</t>
+    <t>http://hl7.org/fhir/ValueSet/clinical-findings|4.0.1</t>
   </si>
   <si>
     <t>inboundRelationship[typeCode=SPRT].source[classCode=OBS, moodCode=EVN, code=LOINC:54531-9].value (type=CD)</t>
